--- a/output/感染症対策委員会_研修実施報告書_R8.6.20.xlsx
+++ b/output/感染症対策委員会_研修実施報告書_R8.6.20.xlsx
@@ -79,7 +79,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -101,11 +101,44 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -131,6 +164,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,7 +531,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:D32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -508,28 +542,28 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>株式会社dhpケアマネジメント</t>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>感染症対策委員会 研修実施報告書（統合版）</t>
+          <t>感染症対策委員会 研修・訓練実施報告書（統合版）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1．研修実施報告書</t>
+          <t>1．研修・訓練実施報告書</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>■ 研修日時</t>
+          <t>■ 研修・訓練日時</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -537,12 +571,12 @@
           <t>令和8年6月20日　14時00分～16時00分</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="11" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>■ 研修内容</t>
+          <t>■ 研修・訓練内容</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -550,12 +584,12 @@
           <t>感染症・食中毒の予防および発生時対応、BCP運用手順、委員会連携強化</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
+      <c r="D7" s="11" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>■ 研修場所</t>
+          <t>■ 実施場所</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -563,7 +597,7 @@
           <t>株式会社dhpケアマネジメント 本社会議スペース（オンライン併用）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="11" t="n"/>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
@@ -577,12 +611,12 @@
 医療的助言：松村（看護職委員）</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
+      <c r="D9" s="11" t="n"/>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>■ 研修参加者</t>
+          <t>■ 参加者</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -591,7 +625,7 @@
 委員：松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="11" t="n"/>
     </row>
     <row r="11" ht="152" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
@@ -609,7 +643,7 @@
 ・理解度チェックシートの提出</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="D11" s="11" t="n"/>
     </row>
     <row r="12" ht="152" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
@@ -619,11 +653,11 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>今回の夏季感染対策研修では、委員会メンバー全員が一丸となり、初動対応・ゾーンニング・BCP運用の要点を明確に整理できたことが大きな成果でした。特に、想定訓練において動線遮断やPPE装着といった具体的オペレーションを確認したことにより、実際の発生時に迷いが生じにくい体制が構築できています。
-課題として浮き彫りになったPPE配置の分かりづらさや、判断基準の統一については、委員として責任を持って改善し、現場にとってより安全で実務的な仕組みへ進化させていきます。今後も“早期把握・早期遮断・正確な対応”を軸に、利用者とスタッフ双方の安全を守り抜く体制づくりを進めていきます。</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
+          <t>今回の夏季感染対策研修では、委員会メンバー全員が一丸となり、初動対応・感染疑い時の訪問調整・BCP運用の要点を明確に整理できたことが大きな成果でした。特に、想定訓練において感染疑い利用者宅への訪問調整（担当者限定・訪問順の変更）やPPE装着といった具体的オペレーションを確認したことにより、実際の発生時に迷いが生じにくい体制が構築できています。
+課題として浮き彫りになった訪問用衛生用品セットの内容・在庫の分かりづらさや、判断基準の統一については、委員として責任を持って改善し、現場にとってより安全で実務的な仕組みへ進化させていきます。今後も“早期把握・早期遮断・正確な対応”を軸に、利用者とスタッフ双方の安全を守り抜く体制づくりを進めていきます。</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
@@ -636,7 +670,7 @@
           <t>令和8年6月20日</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="11" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
@@ -649,7 +683,7 @@
           <t>生田友哉</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="11" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
@@ -682,7 +716,7 @@
 ・季節性ウイルスと新規感染症の混在期への備え</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
+      <c r="D18" s="11" t="n"/>
     </row>
     <row r="19" ht="98" customHeight="1">
       <c r="B19" s="8" t="inlineStr">
@@ -694,12 +728,12 @@
         <is>
           <t>・生田：統括
 ・松村：トリアージ・医療的助言
-・吉田（俊）：導線遮断・ゾーニング
+・吉田（俊）：感染疑い時の訪問調整（担当者限定・訪問順の変更）
 ・吉田（麻）：行政報告ルート確認
 ・win yadanar aung：研修体系化と欠席フォロー</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
+      <c r="D19" s="11" t="n"/>
     </row>
     <row r="20" ht="80" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
@@ -715,7 +749,7 @@
 ・クラスター発生時の業務継続判断</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n"/>
+      <c r="D20" s="11" t="n"/>
     </row>
     <row r="21" ht="62" customHeight="1">
       <c r="B21" s="8" t="inlineStr">
@@ -726,11 +760,11 @@
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>・グローブ二重装着
-・ガウン着脱の注意点
-・廃棄物処理とゾーニング</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
+・ガウン着脱の注意点（利用者宅の玄関等での着脱手順）
+・使用済みPPE・廃棄物の密閉処理（利用者宅のごみ出しルールに従う）</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="B22" s="8" t="inlineStr">
@@ -740,12 +774,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>・温度管理
-・搬入物検品
+          <t>・調理援助時の温度管理
+・購入食品・冷蔵庫内食品の消費期限確認
 ・嘔吐物処理手順</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n"/>
+      <c r="D22" s="11" t="n"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="B23" s="8" t="inlineStr">
@@ -755,12 +789,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>・巡回チェック表簡素化
+          <t>・訪問時の体調確認チェック表の簡素化
 ・月次ミニ研修
 ・行政書類テンプレ改善</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
+      <c r="D23" s="11" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
@@ -777,13 +811,13 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>・導線遮断に3分の遅れ
-・PPE在庫の把握に差
+          <t>・感染疑い時の訪問調整（担当者限定・訪問順の変更）の判断に3分の遅れ
+・訪問用PPE・衛生用品の在庫把握に差
 ・嘔吐物処理セットの補充漏れ
 ・BCPレベル判断の迷い</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
+      <c r="D26" s="11" t="n"/>
     </row>
     <row r="27" ht="70" customHeight="1">
       <c r="B27" s="4" t="inlineStr">
@@ -793,13 +827,13 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>・初動カードを電話横へ配置
-・PPE棚の色分け・写真表示
+          <t>・初動カードを事業所の電話横へ配置し、訪問用バッグにも携行
+・訪問用衛生用品セットの中身を写真付きで一覧表示
 ・嘔吐物処理セットの月2回点検
 ・BCP基準は生田・松村の2名承認制</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
+      <c r="D27" s="11" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
@@ -819,12 +853,12 @@
           <t>委員会メンバー全員（5名）</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D30" s="11" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>5. 訓練実施責任者</t>
+          <t>5. 研修・訓練実施責任者</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -832,12 +866,12 @@
           <t>委員長：生田友哉</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D31" s="11" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>6. 訓練記録作成者</t>
+          <t>6. 研修・訓練記録作成者</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -845,7 +879,7 @@
           <t>生田友哉</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n"/>
+      <c r="D32" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -865,8 +899,8 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B3:D3"/>

--- a/output/感染症対策委員会_研修実施報告書_R8.6.20.xlsx
+++ b/output/感染症対策委員会_研修実施報告書_R8.6.20.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -539,6 +539,7 @@
     <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -553,6 +554,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -622,7 +624,7 @@
       <c r="C10" s="5" t="inlineStr">
         <is>
           <t>委員長：生田友哉
-委員：松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
+委員：松村知恵、WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -685,6 +687,7 @@
       </c>
       <c r="D14" s="11" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -730,7 +733,7 @@
 ・松村：トリアージ・医療的助言
 ・吉田（俊）：感染疑い時の訪問調整（担当者限定・訪問順の変更）
 ・吉田（麻）：行政報告ルート確認
-・win yadanar aung：研修体系化と欠席フォロー</t>
+・WIN YADANAR AUNG：研修体系化と欠席フォロー</t>
         </is>
       </c>
       <c r="D19" s="11" t="n"/>
@@ -796,6 +799,7 @@
       </c>
       <c r="D23" s="11" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -835,6 +839,7 @@
       </c>
       <c r="D27" s="11" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>

--- a/output/感染症対策委員会_研修実施報告書_R8.6.20.xlsx
+++ b/output/感染症対策委員会_研修実施報告書_R8.6.20.xlsx
@@ -624,7 +624,7 @@
       <c r="C10" s="5" t="inlineStr">
         <is>
           <t>委員長：生田友哉
-委員：松村知恵、WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
+委員：松村知恵、WIN YADANAR AUNG、吉田駿成、吉田麻美</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -731,7 +731,7 @@
         <is>
           <t>・生田：統括
 ・松村：トリアージ・医療的助言
-・吉田（俊）：感染疑い時の訪問調整（担当者限定・訪問順の変更）
+・吉田（駿）：感染疑い時の訪問調整（担当者限定・訪問順の変更）
 ・吉田（麻）：行政報告ルート確認
 ・WIN YADANAR AUNG：研修体系化と欠席フォロー</t>
         </is>

--- a/output/感染症対策委員会_研修実施報告書_R8.6.20.xlsx
+++ b/output/感染症対策委員会_研修実施報告書_R8.6.20.xlsx
@@ -528,9 +528,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="B2:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,6 @@
     <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -554,7 +553,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -687,7 +685,6 @@
       </c>
       <c r="D14" s="11" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -799,7 +796,6 @@
       </c>
       <c r="D23" s="11" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -839,7 +835,6 @@
       </c>
       <c r="D27" s="11" t="n"/>
     </row>
-    <row r="28"/>
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -916,6 +911,8 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>